--- a/laporan_padel_dki_jakarta_2026-10-03.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-03.xlsx
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp19.260.000</t>
+          <t>Rp19.350.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.685.000</t>
+          <t>Rp6.985.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.680.000</t>
+          <t>Rp3.780.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.860.000</t>
+          <t>Rp5.130.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-03.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-03.xlsx
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.955.000</t>
+          <t>Rp4.279.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.890.000</t>
+          <t>Rp2.740.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.015.000</t>
+          <t>Rp3.195.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp365.000</t>
+          <t>Rp490.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>54</v>
       </c>
       <c r="D58" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp860.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.590.000</t>
+          <t>Rp1.908.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp15.560.000</t>
+          <t>Rp16.338.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp75.000 - Rp99.000</t>
         </is>
       </c>
     </row>
@@ -4594,16 +4594,16 @@
         <v>75</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.020.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.700.000</t>
+          <t>Rp8.750.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp935.000</t>
+          <t>Rp1.033.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D58" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>45</v>
       </c>
       <c r="D60" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>36</v>
       </c>
       <c r="D61" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D63" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D66" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp8.750.000</t>
+          <t>Rp9.600.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.075.000</t>
+          <t>Rp2.325.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp19.350.000</t>
+          <t>Rp19.440.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.850.000</t>
+          <t>Rp16.575.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.325.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp21.505.000</t>
+          <t>Rp21.804.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp38.500.000</t>
+          <t>Rp39.100.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.325.000</t>
+          <t>Rp5.475.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.908.000</t>
+          <t>Rp2.226.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.060.000</t>
+          <t>Rp1.290.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.985.000</t>
+          <t>Rp7.180.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.963.500</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.865.000</t>
+          <t>Rp4.520.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.675.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.665.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp845.000</t>
+          <t>Rp1.014.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.780.000</t>
+          <t>Rp3.960.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-03.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-03.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.470.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.279.000</t>
+          <t>Rp4.448.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.576.000</t>
+          <t>Rp3.725.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp15.463.500</t>
+          <t>Rp16.013.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.325.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp5.760.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp996.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>168</v>
       </c>
       <c r="D22" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp16.592.000</t>
+          <t>Rp17.090.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.740.000</t>
+          <t>Rp3.040.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.189.000</t>
+          <t>Rp1.564.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.720.000</t>
+          <t>Rp3.920.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.270.000</t>
+          <t>Rp3.390.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.967.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.020.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1660,21 +1660,21 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.580.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rp210.000</t>
+          <t>Rp150.000 - Rp210.000</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.032.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.908.000</t>
+          <t>Rp2.108.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>30</v>
       </c>
       <c r="D64" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp118.000</t>
+          <t>Rp236.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>36</v>
       </c>
       <c r="D66" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp13.364.000</t>
+          <t>Rp13.563.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.765.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp9.830.000</t>
+          <t>Rp9.390.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>85</v>
       </c>
       <c r="D81" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.782.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp8.580.000</t>
+          <t>Rp8.780.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp20.866.500</t>
+          <t>Rp21.218.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp16.338.000</t>
+          <t>Rp17.894.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp10.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.005.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp4.775.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.625.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.785.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4329,7 +4329,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rp115.000</t>
+          <t>Rp110.000 - Rp115.000</t>
         </is>
       </c>
     </row>
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp22.200.000</t>
+          <t>Rp22.690.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp19.150.000</t>
+          <t>Rp19.300.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>54</v>
       </c>
       <c r="D44" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4975,12 +4975,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp200.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.985.000</t>
+          <t>Rp3.582.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.260.000</t>
+          <t>Rp7.920.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>112</v>
       </c>
       <c r="D55" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.033.000</t>
+          <t>Rp1.131.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>51</v>
       </c>
       <c r="D57" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D64" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.970.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>84</v>
       </c>
       <c r="D65" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp5.695.000</t>
+          <t>Rp6.145.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp1.640.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp25.750.000</t>
+          <t>Rp28.150.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.872.000</t>
+          <t>Rp5.040.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp19.440.000</t>
+          <t>Rp20.020.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.680.000</t>
+          <t>Rp12.830.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.595.000</t>
+          <t>Rp12.745.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp198.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp16.995.000</t>
+          <t>Rp17.190.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.575.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.682.000</t>
+          <t>Rp2.831.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.885.000</t>
+          <t>Rp7.452.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp640.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp13.300.000</t>
+          <t>Rp14.200.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>108</v>
       </c>
       <c r="D35" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp447.000</t>
+          <t>Rp596.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>128</v>
       </c>
       <c r="D40" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp598.000</t>
+          <t>Rp1.794.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp7.150.000</t>
+          <t>Rp7.700.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>36</v>
       </c>
       <c r="D46" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp7.620.000</t>
+          <t>Rp8.120.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>102</v>
       </c>
       <c r="D48" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.475.000</t>
+          <t>Rp5.825.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp17.690.000</t>
+          <t>Rp18.450.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp6.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.370.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.445.000</t>
+          <t>Rp11.005.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.310.000</t>
+          <t>Rp2.772.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp570.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.520.000</t>
+          <t>Rp22.320.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.425.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.360.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.599.972</t>
+          <t>Rp5.999.970</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp4.410.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.835.000</t>
+          <t>Rp4.495.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.495.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.035.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.130.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>72</v>
       </c>
       <c r="D41" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.960.000</t>
+          <t>Rp4.140.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.260.000</t>
+          <t>Rp4.430.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-03.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-03.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp1.820.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp704.000</t>
+          <t>Rp1.144.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp11.980.000</t>
+          <t>Rp12.980.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.725.000</t>
+          <t>Rp3.278.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.013.500</t>
+          <t>Rp17.498.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.760.000</t>
+          <t>Rp5.920.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>170</v>
       </c>
       <c r="D17" t="n">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.380.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp996.000</t>
+          <t>Rp1.743.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp16.885.000</t>
+          <t>Rp17.835.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>168</v>
       </c>
       <c r="D22" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp17.090.000</t>
+          <t>Rp19.486.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.920.000</t>
+          <t>Rp4.160.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.541.000</t>
+          <t>Rp2.901.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.483.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.960.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.802.000</t>
+          <t>Rp3.098.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.020.000</t>
+          <t>Rp2.830.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp7.697.000</t>
+          <t>Rp7.160.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp4.692.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.520.000</t>
+          <t>Rp1.260.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp950.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>96</v>
       </c>
       <c r="D48" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp8.752.000</t>
+          <t>Rp8.983.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.075.000</t>
+          <t>Rp4.315.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>56</v>
       </c>
       <c r="D51" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.320.000</t>
+          <t>Rp4.608.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>28</v>
       </c>
       <c r="D53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp2.277.000</t>
+          <t>Rp1.782.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp490.000</t>
+          <t>Rp605.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.420.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.108.000</t>
+          <t>Rp2.208.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp13.563.000</t>
+          <t>Rp14.460.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.720.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.670.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp9.390.000</t>
+          <t>Rp8.410.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.275.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp1.975.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2931,21 +2931,21 @@
         <v>85</v>
       </c>
       <c r="D81" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp5.050.000</t>
+          <t>Rp5.377.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp109.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp1.782.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>108</v>
       </c>
       <c r="D86" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>28</v>
       </c>
       <c r="D93" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp646.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp8.780.000</t>
+          <t>Rp9.020.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.470.000</t>
+          <t>Rp1.920.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3489,16 +3489,16 @@
         <v>32</v>
       </c>
       <c r="D99" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.106.000</t>
+          <t>Rp2.187.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>133</v>
       </c>
       <c r="D3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp21.218.500</t>
+          <t>Rp21.394.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp17.894.000</t>
+          <t>Rp21.006.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp10.000.000</t>
+          <t>Rp10.350.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>90</v>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.435.000</t>
+          <t>Rp6.840.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.775.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp5.125.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.775.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp22.690.000</t>
+          <t>Rp24.085.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.875.000</t>
+          <t>Rp6.325.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>75</v>
       </c>
       <c r="D35" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.020.000</t>
+          <t>Rp5.520.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp19.300.000</t>
+          <t>Rp20.850.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>48</v>
       </c>
       <c r="D38" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>68</v>
       </c>
       <c r="D41" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D49" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp7.920.000</t>
+          <t>Rp8.470.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.131.000</t>
+          <t>Rp1.277.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp470.000</t>
+          <t>Rp1.255.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>162</v>
       </c>
       <c r="D69" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp11.050.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp10.780.000</t>
+          <t>Rp11.357.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.350.000</t>
+          <t>Rp8.650.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.640.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp28.150.000</t>
+          <t>Rp30.600.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.325.000</t>
+          <t>Rp2.725.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp940.000</t>
+          <t>Rp1.128.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp20.020.000</t>
+          <t>Rp20.400.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp336.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp17.190.000</t>
+          <t>Rp17.660.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp18.135.000</t>
+          <t>Rp18.580.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.575.000</t>
+          <t>Rp17.250.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp7.625.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.850.000</t>
+          <t>Rp19.850.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>68</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp1.755.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp14.200.000</t>
+          <t>Rp14.650.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.384.000</t>
+          <t>Rp3.948.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.225.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp21.804.000</t>
+          <t>Rp23.000.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>128</v>
       </c>
       <c r="D40" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.794.000</t>
+          <t>Rp2.392.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp7.700.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>102</v>
       </c>
       <c r="D48" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.350.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.825.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.450.000</t>
+          <t>Rp19.110.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp3.175.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.370.000</t>
+          <t>Rp3.630.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp11.005.000</t>
+          <t>Rp12.045.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.599.982</t>
+          <t>Rp4.399.978</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.772.000</t>
+          <t>Rp3.118.500</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp570.000</t>
+          <t>Rp1.480.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.520.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.570.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.999.970</t>
+          <t>Rp6.199.969</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.225.000</t>
+          <t>Rp4.400.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.495.000</t>
+          <t>Rp5.430.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp4.460.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.035.000</t>
+          <t>Rp2.405.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.670.000</t>
+          <t>Rp5.940.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp6.350.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp4.140.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.430.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-03.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-03.xlsx
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp17.498.500</t>
+          <t>Rp17.636.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.483.000</t>
+          <t>Rp3.612.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.098.000</t>
+          <t>Rp3.294.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.195.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>18</v>
       </c>
       <c r="D56" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp447.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp6.900.000</t>
+          <t>Rp7.100.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.275.000</t>
+          <t>Rp3.350.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp2.145.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>47</v>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.840.000</t>
+          <t>Rp7.590.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.125.000</t>
+          <t>Rp4.995.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.148.000</t>
+          <t>Rp2.267.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp20.400.000</t>
+          <t>Rp20.490.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp12.830.000</t>
+          <t>Rp12.950.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp336.000</t>
+          <t>Rp474.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.452.000</t>
+          <t>Rp7.938.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.582.000</t>
+          <t>Rp3.781.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp14.650.000</t>
+          <t>Rp15.850.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>180</v>
       </c>
       <c r="D36" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.925.000</t>
+          <t>Rp6.525.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp23.000.000</t>
+          <t>Rp23.200.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.175.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.460.000</t>
+          <t>Rp4.655.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.940.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp6.650.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
